--- a/data/demo/output/品質分析.xlsx
+++ b/data/demo/output/品質分析.xlsx
@@ -94588,7 +94588,7 @@
         </is>
       </c>
       <c r="B3" s="3" t="n">
-        <v>46306.38185185185</v>
+        <v>46306.3869212963</v>
       </c>
     </row>
     <row r="4">
